--- a/District_GIS_Parakh_CMMI_L5_Artifacts/District GIS Parakh Artefacts/MP Cooperative/New Latest Updated final format from department/Updated - UserListTemplate_First_Last_Name_Separated (1).xlsx
+++ b/District_GIS_Parakh_CMMI_L5_Artifacts/District GIS Parakh Artefacts/MP Cooperative/New Latest Updated final format from department/Updated - UserListTemplate_First_Last_Name_Separated (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Organization_Docs\District_GIS_Parakh_CMMI_L5_Artifacts\District GIS Parakh Artefacts\MP Cooperative\New Latest Updated final format from department\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19C947A-DC8D-489F-9CA9-E1D84FA37BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF32ACB0-BA9F-4703-B4A3-7CD0E79E4D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="570">
   <si>
     <t>Sno.</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>Email</t>
-  </si>
-  <si>
-    <t>UserName</t>
   </si>
   <si>
     <t>Designation Name</t>
@@ -2185,7 +2182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.77734375" customWidth="1"/>
@@ -2194,20 +2191,18 @@
     <col min="4" max="4" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.77734375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="56.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" customWidth="1"/>
-    <col min="14" max="14" width="22.5546875" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" customWidth="1"/>
-    <col min="16" max="16" width="22" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22" customWidth="1"/>
-    <col min="18" max="18" width="56.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="11" max="11" width="41.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.77734375" customWidth="1"/>
+    <col min="13" max="13" width="22.5546875" customWidth="1"/>
+    <col min="14" max="14" width="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="56.5546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2221,683 +2216,629 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>537</v>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>536</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>535</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="9" t="str">
+      <c r="H2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="9" t="str">
         <f>_xlfn.CONCAT(E2,"_",F2)</f>
         <v>PRADEEP_KUMAR_RAWAT</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
       <c r="N2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="9" t="str">
-        <f t="shared" ref="G3:G66" si="0">_xlfn.CONCAT(E3,"_",F3)</f>
-        <v>SURESH_Sawle</v>
-      </c>
       <c r="H3" s="5" t="s">
-        <v>570</v>
+        <v>18</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" s="9" t="str">
+        <f>_xlfn.CONCAT(E3,"_",F3)</f>
+        <v>SURESH_Sawle</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
       <c r="N3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>482</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="9" t="str">
-        <f t="shared" si="0"/>
+      <c r="H4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="9" t="str">
+        <f>_xlfn.CONCAT(E4,"_",F4)</f>
         <v>YOGITA_VERMA</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="N4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="P4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SAURABH_KOTHIYA</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J5" s="5"/>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="9" t="str">
+        <f>_xlfn.CONCAT(E5,"_",F5)</f>
+        <v>SAURABH_KOTHIYA</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>AKHILESH_SHUKLA</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="5" t="s">
+      <c r="J6" s="5"/>
+      <c r="K6" s="9" t="str">
+        <f>_xlfn.CONCAT(E6,"_",F6)</f>
+        <v>AKHILESH_SHUKLA</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q6" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>BASUDEV_Singh_Bhadouriya</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="J7" s="5"/>
+      <c r="K7" s="9" t="str">
+        <f>_xlfn.CONCAT(E7,"_",F7)</f>
+        <v>BASUDEV_Singh_Bhadouriya</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>RAJYASH_VARDHAN_KURIL</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="5" t="s">
+      <c r="J8" s="5"/>
+      <c r="K8" s="9" t="str">
+        <f>_xlfn.CONCAT(E8,"_",F8)</f>
+        <v>RAJYASH_VARDHAN_KURIL</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="P8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q8" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>ARUN_KUMAR_MASRAM</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="5" t="s">
+      <c r="J9" s="5"/>
+      <c r="K9" s="9" t="str">
+        <f>_xlfn.CONCAT(E9,"_",F9)</f>
+        <v>ARUN_KUMAR_MASRAM</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="P9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PAYAL_ASATKAR</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="9" t="str">
+        <f>_xlfn.CONCAT(E10,"_",F10)</f>
+        <v>PAYAL_ASATKAR</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="N10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Raju_Dawar</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="5" t="s">
+      <c r="J11" s="5"/>
+      <c r="K11" s="9" t="str">
+        <f>_xlfn.CONCAT(E11,"_",F11)</f>
+        <v>Raju_Dawar</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="P11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>AKHILESH_KUMAR_NIGAM</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="5" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="9" t="str">
+        <f>_xlfn.CONCAT(E12,"_",F12)</f>
+        <v>AKHILESH_KUMAR_NIGAM</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="P12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q12" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>ARTI_PATEL</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="9" t="str">
+        <f>_xlfn.CONCAT(E13,"_",F13)</f>
+        <v>ARTI_PATEL</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -2905,3168 +2846,2928 @@
         <v>390011349</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>ARUN_KUMAR_MISHRA</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="5" t="s">
+      <c r="J14" s="5"/>
+      <c r="K14" s="9" t="str">
+        <f>_xlfn.CONCAT(E14,"_",F14)</f>
+        <v>ARUN_KUMAR_MISHRA</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q14" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>DEVENDRA_PRATAP_SINGH</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="5" t="s">
+      <c r="J15" s="5"/>
+      <c r="K15" s="9" t="str">
+        <f>_xlfn.CONCAT(E15,"_",F15)</f>
+        <v>DEVENDRA_PRATAP_SINGH</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
       <c r="N15" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q15" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G16" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>GOPAL_PRASAD_PRAJAPATI</v>
-      </c>
       <c r="H16" s="5" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="5" t="s">
+      <c r="J16" s="5"/>
+      <c r="K16" s="9" t="str">
+        <f>_xlfn.CONCAT(E16,"_",F16)</f>
+        <v>GOPAL_PRASAD_PRAJAPATI</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="P16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q16" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>GUNJAN_RAI</v>
-      </c>
       <c r="H17" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="9" t="str">
+        <f>_xlfn.CONCAT(E17,"_",F17)</f>
+        <v>GUNJAN_RAI</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="N17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q17" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>HITENDRA_SINGH_WAGHELA</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="9" t="str">
+        <f>_xlfn.CONCAT(E18,"_",F18)</f>
+        <v>HITENDRA_SINGH_WAGHELA</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="N18" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q18" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>JYOTI_KUMBHARE</v>
-      </c>
       <c r="H19" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="9" t="str">
+        <f>_xlfn.CONCAT(E19,"_",F19)</f>
+        <v>JYOTI_KUMBHARE</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N19" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>KRITI_SAKSENA</v>
-      </c>
       <c r="H20" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="9" t="str">
+        <f>_xlfn.CONCAT(E20,"_",F20)</f>
+        <v>KRITI_SAKSENA</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="N20" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R20" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="G21" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>RAJKUMAR_PATIL</v>
-      </c>
       <c r="H21" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="5" t="s">
+      <c r="J21" s="5"/>
+      <c r="K21" s="9" t="str">
+        <f>_xlfn.CONCAT(E21,"_",F21)</f>
+        <v>RAJKUMAR_PATIL</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="P21" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q21" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G22" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>RAMA_SHANKAR_VISHVAKARMA</v>
-      </c>
       <c r="H22" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="J22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="9" t="str">
+        <f>_xlfn.CONCAT(E22,"_",F22)</f>
+        <v>RAMA_SHANKAR_VISHVAKARMA</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N22" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O22" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R22" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="G23" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SHIVENDRA_DEO_PANDEY</v>
-      </c>
       <c r="H23" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="9" t="str">
+        <f>_xlfn.CONCAT(E23,"_",F23)</f>
+        <v>SHIVENDRA_DEO_PANDEY</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="N23" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q23" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SHWETA_RAWAT</v>
-      </c>
       <c r="H24" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="J24" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="9" t="str">
+        <f>_xlfn.CONCAT(E24,"_",F24)</f>
+        <v>SHWETA_RAWAT</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q24" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R24" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>VAISHALY_JAIN</v>
-      </c>
       <c r="H25" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="J25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="9" t="str">
+        <f>_xlfn.CONCAT(E25,"_",F25)</f>
+        <v>VAISHALY_JAIN</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q25" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R25" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>VIMAL_KUMAR_SRIVASTAVA</v>
-      </c>
       <c r="H26" s="5" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="J26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="9" t="str">
+        <f>_xlfn.CONCAT(E26,"_",F26)</f>
+        <v>VIMAL_KUMAR_SRIVASTAVA</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="N26" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q26" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R26" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G27" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>YATISH_TRIPATHI</v>
-      </c>
       <c r="H27" s="5" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" s="5" t="s">
+      <c r="J27" s="5"/>
+      <c r="K27" s="9" t="str">
+        <f>_xlfn.CONCAT(E27,"_",F27)</f>
+        <v>YATISH_TRIPATHI</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="P27" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P27" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q27" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R27" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G28" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>MANOJ_KUMAR_JAISWAL</v>
-      </c>
       <c r="H28" s="5" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="J28" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K28" s="5" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="9" t="str">
+        <f>_xlfn.CONCAT(E28,"_",F28)</f>
+        <v>MANOJ_KUMAR_JAISWAL</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="P28" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P28" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q28" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="R28" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G29" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Chandra_pratap_Singh_Bhadoria</v>
-      </c>
       <c r="H29" s="5" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="J29" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" s="5" t="s">
+      <c r="J29" s="5"/>
+      <c r="K29" s="9" t="str">
+        <f>_xlfn.CONCAT(E29,"_",F29)</f>
+        <v>Chandra_pratap_Singh_Bhadoria</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="P29" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P29" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q29" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="R29" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G30" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>NANCY_RAGHUWANSHI</v>
-      </c>
       <c r="H30" s="5" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="9" t="str">
+        <f>_xlfn.CONCAT(E30,"_",F30)</f>
+        <v>NANCY_RAGHUWANSHI</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="N30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>517</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q30" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="R30" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G31" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>GORDHANLAL_SOLANKI</v>
-      </c>
       <c r="H31" s="5" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="J31" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" s="5" t="s">
+      <c r="J31" s="5"/>
+      <c r="K31" s="9" t="str">
+        <f>_xlfn.CONCAT(E31,"_",F31)</f>
+        <v>GORDHANLAL_SOLANKI</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="P31" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="R31" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G32" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>DIVYA_NAMDEV</v>
-      </c>
       <c r="H32" s="5" t="s">
-        <v>186</v>
+        <v>33</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="J32" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K32" s="5" t="s">
+      <c r="J32" s="5"/>
+      <c r="K32" s="9" t="str">
+        <f>_xlfn.CONCAT(E32,"_",F32)</f>
+        <v>DIVYA_NAMDEV</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="P32" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P32" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="R32" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G33" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>RAJESH_UIKE</v>
-      </c>
       <c r="H33" s="5" t="s">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="J33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="5" t="s">
+      <c r="J33" s="5"/>
+      <c r="K33" s="9" t="str">
+        <f>_xlfn.CONCAT(E33,"_",F33)</f>
+        <v>RAJESH_UIKE</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="P33" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P33" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="R33" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G34" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>KEERTI KUMAR_SHIV</v>
-      </c>
       <c r="H34" s="5" t="s">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="J34" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" s="5" t="s">
+      <c r="J34" s="5"/>
+      <c r="K34" s="9" t="str">
+        <f>_xlfn.CONCAT(E34,"_",F34)</f>
+        <v>KEERTI KUMAR_SHIV</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="P34" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P34" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q34" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="R34" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G35" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>CHHAVIKANT_WAGHMARE</v>
-      </c>
       <c r="H35" s="5" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="J35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" s="5" t="s">
+      <c r="J35" s="5"/>
+      <c r="K35" s="9" t="str">
+        <f>_xlfn.CONCAT(E35,"_",F35)</f>
+        <v>CHHAVIKANT_WAGHMARE</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="P35" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q35" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R35" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SATISH KUMAR_BATHAM</v>
-      </c>
       <c r="H36" s="5" t="s">
-        <v>204</v>
+        <v>18</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="J36" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="9" t="str">
+        <f>_xlfn.CONCAT(E36,"_",F36)</f>
+        <v>SATISH KUMAR_BATHAM</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="N36" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q36" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R36" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G37" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>AJAYPAL SINGH_BILODIYA</v>
-      </c>
       <c r="H37" s="5" t="s">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="J37" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" s="5" t="s">
+      <c r="J37" s="5"/>
+      <c r="K37" s="9" t="str">
+        <f>_xlfn.CONCAT(E37,"_",F37)</f>
+        <v>AJAYPAL SINGH_BILODIYA</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="P37" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P37" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q37" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="R37" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="G38" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Harshvardhan_Wasnik</v>
-      </c>
       <c r="H38" s="5" t="s">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="J38" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="9" t="str">
+        <f>_xlfn.CONCAT(E38,"_",F38)</f>
+        <v>Harshvardhan_Wasnik</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="N38" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O38" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>449</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q38" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="R38" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G39" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SONAM_SONI</v>
-      </c>
       <c r="H39" s="5" t="s">
-        <v>226</v>
+        <v>33</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="J39" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="5" t="s">
+      <c r="J39" s="5"/>
+      <c r="K39" s="9" t="str">
+        <f>_xlfn.CONCAT(E39,"_",F39)</f>
+        <v>SONAM_SONI</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="P39" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P39" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q39" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="R39" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G40" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>GHANSHYAM_DEHERIYA</v>
-      </c>
       <c r="H40" s="5" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="J40" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="5" t="s">
+      <c r="J40" s="5"/>
+      <c r="K40" s="9" t="str">
+        <f>_xlfn.CONCAT(E40,"_",F40)</f>
+        <v>GHANSHYAM_DEHERIYA</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="P40" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P40" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q40" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="R40" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G41" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>DEEPALI_KHANDELWAL</v>
-      </c>
       <c r="H41" s="5" t="s">
-        <v>238</v>
+        <v>33</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="J41" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K41" s="5" t="s">
+      <c r="J41" s="5"/>
+      <c r="K41" s="9" t="str">
+        <f>_xlfn.CONCAT(E41,"_",F41)</f>
+        <v>DEEPALI_KHANDELWAL</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="P41" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P41" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q41" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="R41" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G42" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PRATYASHA_RAGHUWANSHI</v>
-      </c>
       <c r="H42" s="5" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="J42" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K42" s="5" t="s">
+      <c r="J42" s="5"/>
+      <c r="K42" s="9" t="str">
+        <f>_xlfn.CONCAT(E42,"_",F42)</f>
+        <v>PRATYASHA_RAGHUWANSHI</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="P42" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P42" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q42" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="R42" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G43" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>VARSHA_SHRIWAS</v>
-      </c>
       <c r="H43" s="5" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="J43" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="9" t="str">
+        <f>_xlfn.CONCAT(E43,"_",F43)</f>
+        <v>VARSHA_SHRIWAS</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N43" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O43" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>467</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q43" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="R43" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="G44" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>MUKESH_KUMAR_JAIN</v>
-      </c>
       <c r="H44" s="5" t="s">
-        <v>253</v>
+        <v>18</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="J44" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K44" s="5" t="s">
+      <c r="J44" s="5"/>
+      <c r="K44" s="9" t="str">
+        <f>_xlfn.CONCAT(E44,"_",F44)</f>
+        <v>MUKESH_KUMAR_JAIN</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="P44" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O44" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P44" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q44" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="R44" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G45" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>NARESH_KUMAR_SINHA</v>
-      </c>
       <c r="H45" s="5" t="s">
-        <v>259</v>
+        <v>18</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="J45" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K45" s="5" t="s">
+      <c r="J45" s="5"/>
+      <c r="K45" s="9" t="str">
+        <f>_xlfn.CONCAT(E45,"_",F45)</f>
+        <v>NARESH_KUMAR_SINHA</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="P45" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O45" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P45" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q45" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="R45" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="5" t="s">
+      <c r="E46" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="F46" s="5" t="s">
+      <c r="G46" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G46" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>DINESH_CHANDRA_BHIDE</v>
-      </c>
-      <c r="H46" t="s">
-        <v>265</v>
+      <c r="H46" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="J46" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" s="5" t="s">
+      <c r="J46" s="5"/>
+      <c r="K46" s="9" t="str">
+        <f>_xlfn.CONCAT(E46,"_",F46)</f>
+        <v>DINESH_CHANDRA_BHIDE</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O46" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="P46" t="s">
         <v>264</v>
       </c>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O46" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P46" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q46" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="R46" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="F47" s="5" t="s">
+      <c r="G47" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="G47" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>RAJENDRA_SINGH_KANESH</v>
-      </c>
       <c r="H47" s="5" t="s">
-        <v>265</v>
+        <v>18</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="9" t="str">
+        <f>_xlfn.CONCAT(E47,"_",F47)</f>
+        <v>RAJENDRA_SINGH_KANESH</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N47" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O47" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>488</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q47" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="R47" s="5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="5" t="s">
+      <c r="E48" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="F48" s="5" t="s">
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="G48" s="9" t="str">
-        <f t="shared" si="0"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="9" t="str">
+        <f>_xlfn.CONCAT(E48,"_",F48)</f>
         <v>SANJAY_SINGH_ARYA</v>
       </c>
-      <c r="H48" t="s">
-        <v>275</v>
-      </c>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5" t="s">
+      <c r="L48" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N48" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="P48" t="s">
         <v>274</v>
       </c>
-      <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P48" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q48" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="R48" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G49" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>KASHIRAM_AWASE</v>
-      </c>
       <c r="H49" s="5" t="s">
-        <v>281</v>
+        <v>18</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="J49" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K49" s="5" t="s">
+      <c r="J49" s="5"/>
+      <c r="K49" s="9" t="str">
+        <f>_xlfn.CONCAT(E49,"_",F49)</f>
+        <v>KASHIRAM_AWASE</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="P49" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O49" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P49" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q49" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="R49" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="F50" s="5" t="s">
+      <c r="G50" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G50" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PARMANAND_GODARIA</v>
-      </c>
       <c r="H50" s="5" t="s">
-        <v>287</v>
+        <v>18</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="J50" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K50" s="5" t="s">
+      <c r="J50" s="5"/>
+      <c r="K50" s="9" t="str">
+        <f>_xlfn.CONCAT(E50,"_",F50)</f>
+        <v>PARMANAND_GODARIA</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N50" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="P50" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O50" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P50" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q50" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="R50" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="5" t="s">
+      <c r="E51" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F51" s="5" t="s">
+      <c r="G51" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="G51" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>ANUBHA_SOOD</v>
-      </c>
       <c r="H51" s="5" t="s">
-        <v>293</v>
+        <v>33</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="J51" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K51" s="5" t="s">
+      <c r="J51" s="5"/>
+      <c r="K51" s="9" t="str">
+        <f>_xlfn.CONCAT(E51,"_",F51)</f>
+        <v>ANUBHA_SOOD</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="P51" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O51" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P51" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q51" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="R51" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="5" t="s">
+      <c r="E52" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="F52" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="F52" s="5" t="s">
+      <c r="G52" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G52" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>DINESH_KUMAR_CHOURASIYA</v>
-      </c>
       <c r="H52" s="5" t="s">
-        <v>299</v>
+        <v>18</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="J52" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K52" s="5" t="s">
+      <c r="J52" s="5"/>
+      <c r="K52" s="9" t="str">
+        <f>_xlfn.CONCAT(E52,"_",F52)</f>
+        <v>DINESH_KUMAR_CHOURASIYA</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="P52" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O52" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P52" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q52" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="R52" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="E53" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G53" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SHIVAM_MISHRA</v>
-      </c>
       <c r="H53" s="5" t="s">
-        <v>299</v>
+        <v>18</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="J53" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="9" t="str">
+        <f>_xlfn.CONCAT(E53,"_",F53)</f>
+        <v>SHIVAM_MISHRA</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="N53" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O53" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O53" s="9" t="s">
+        <v>507</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q53" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="R53" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="F54" s="5" t="s">
+      <c r="G54" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G54" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>ANJULI_DHURVE</v>
-      </c>
       <c r="H54" s="5" t="s">
-        <v>309</v>
+        <v>33</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="J54" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K54" s="5" t="s">
+      <c r="J54" s="5"/>
+      <c r="K54" s="9" t="str">
+        <f>_xlfn.CONCAT(E54,"_",F54)</f>
+        <v>ANJULI_DHURVE</v>
+      </c>
+      <c r="L54" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N54" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O54" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="P54" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O54" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P54" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q54" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="R54" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="E55" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="F55" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="G55" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PREM_SINGH_BAROTIYA</v>
-      </c>
       <c r="H55" s="5" t="s">
-        <v>315</v>
+        <v>18</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="J55" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K55" s="5" t="s">
+      <c r="J55" s="5"/>
+      <c r="K55" s="9" t="str">
+        <f>_xlfn.CONCAT(E55,"_",F55)</f>
+        <v>PREM_SINGH_BAROTIYA</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N55" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O55" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="P55" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P55" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q55" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="R55" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="F56" s="5" t="s">
+      <c r="G56" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G56" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>NATUSINGH_BHATI</v>
-      </c>
       <c r="H56" s="5" t="s">
-        <v>321</v>
+        <v>18</v>
       </c>
       <c r="I56" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="J56" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K56" s="5" t="s">
+      <c r="J56" s="5"/>
+      <c r="K56" s="9" t="str">
+        <f>_xlfn.CONCAT(E56,"_",F56)</f>
+        <v>NATUSINGH_BHATI</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N56" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O56" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="P56" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O56" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P56" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q56" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="R56" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" s="5" t="s">
+      <c r="E57" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F57" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="F57" s="5" t="s">
+      <c r="G57" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="G57" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SUDHIR_KAITHWAS</v>
-      </c>
       <c r="H57" s="5" t="s">
-        <v>327</v>
+        <v>18</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="J57" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K57" s="5" t="s">
+      <c r="J57" s="5"/>
+      <c r="K57" s="9" t="str">
+        <f>_xlfn.CONCAT(E57,"_",F57)</f>
+        <v>SUDHIR_KAITHWAS</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N57" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O57" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="P57" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O57" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P57" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q57" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="R57" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="5" t="s">
+      <c r="E58" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="F58" s="5" t="s">
+      <c r="G58" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="G58" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>PRAFUL_LAVAHE</v>
-      </c>
       <c r="H58" s="5" t="s">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="J58" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K58" s="5" t="s">
+      <c r="J58" s="5"/>
+      <c r="K58" s="9" t="str">
+        <f>_xlfn.CONCAT(E58,"_",F58)</f>
+        <v>PRAFUL_LAVAHE</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N58" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O58" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="P58" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="L58" s="5"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O58" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P58" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q58" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="R58" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="G59" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>OM_PRAKASH_GUPTA</v>
-      </c>
       <c r="H59" s="5" t="s">
-        <v>339</v>
+        <v>18</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="J59" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K59" s="5" t="s">
+      <c r="J59" s="5"/>
+      <c r="K59" s="9" t="str">
+        <f>_xlfn.CONCAT(E59,"_",F59)</f>
+        <v>OM_PRAKASH_GUPTA</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N59" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O59" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="P59" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="L59" s="5"/>
-      <c r="M59" s="5"/>
-      <c r="N59" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O59" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P59" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q59" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="R59" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="5" t="s">
+      <c r="E60" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="F60" s="5" t="s">
+      <c r="G60" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G60" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>DEEPTI_BANWASI</v>
-      </c>
       <c r="H60" s="5" t="s">
-        <v>345</v>
+        <v>33</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="J60" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K60" s="5" t="s">
+      <c r="J60" s="5"/>
+      <c r="K60" s="9" t="str">
+        <f>_xlfn.CONCAT(E60,"_",F60)</f>
+        <v>DEEPTI_BANWASI</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N60" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O60" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="P60" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O60" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P60" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q60" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="R60" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="G61" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SHIV_PRAKASH_KAUSHIK</v>
-      </c>
       <c r="H61" s="5" t="s">
-        <v>351</v>
+        <v>18</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="J61" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K61" s="5" t="s">
+      <c r="J61" s="5"/>
+      <c r="K61" s="9" t="str">
+        <f>_xlfn.CONCAT(E61,"_",F61)</f>
+        <v>SHIV_PRAKASH_KAUSHIK</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O61" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="P61" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O61" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P61" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q61" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="R61" s="5" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="G62" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>SANJAY_KAUSHAL</v>
-      </c>
       <c r="H62" s="5" t="s">
-        <v>357</v>
+        <v>18</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="J62" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K62" s="5" t="s">
+      <c r="J62" s="5"/>
+      <c r="K62" s="9" t="str">
+        <f>_xlfn.CONCAT(E62,"_",F62)</f>
+        <v>SANJAY_KAUSHAL</v>
+      </c>
+      <c r="L62" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O62" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="P62" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O62" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P62" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q62" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="R62" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="5" t="s">
+      <c r="E63" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="F63" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="F63" s="5" t="s">
+      <c r="G63" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G63" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>DHRUV_KUMAR_JHARIYA</v>
-      </c>
       <c r="H63" s="5" t="s">
-        <v>363</v>
+        <v>18</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="J63" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K63" s="5" t="s">
+      <c r="J63" s="5"/>
+      <c r="K63" s="9" t="str">
+        <f>_xlfn.CONCAT(E63,"_",F63)</f>
+        <v>DHRUV_KUMAR_JHARIYA</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N63" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="P63" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O63" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P63" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q63" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="R63" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="5" t="s">
+      <c r="E64" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="F64" s="5" t="s">
+      <c r="G64" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G64" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>KANTI_KUMAR_DWIVEDI</v>
-      </c>
       <c r="H64" s="5" t="s">
-        <v>369</v>
+        <v>18</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="J64" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K64" s="5" t="s">
+      <c r="J64" s="5"/>
+      <c r="K64" s="9" t="str">
+        <f>_xlfn.CONCAT(E64,"_",F64)</f>
+        <v>KANTI_KUMAR_DWIVEDI</v>
+      </c>
+      <c r="L64" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N64" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O64" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="P64" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O64" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P64" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q64" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="R64" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="F65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="G65" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>ANITA_UIKEY</v>
-      </c>
       <c r="H65" s="5" t="s">
-        <v>375</v>
+        <v>33</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="J65" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K65" s="5" t="s">
+      <c r="J65" s="5"/>
+      <c r="K65" s="9" t="str">
+        <f>_xlfn.CONCAT(E65,"_",F65)</f>
+        <v>ANITA_UIKEY</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N65" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O65" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="P65" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O65" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P65" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q65" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="R65" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66" s="5" t="s">
+      <c r="E66" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="F66" s="5" t="s">
+      <c r="G66" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="G66" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>BHANWAR_LAL_MAKWANA</v>
-      </c>
       <c r="H66" s="5" t="s">
-        <v>381</v>
+        <v>18</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="J66" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K66" s="5" t="s">
+      <c r="J66" s="5"/>
+      <c r="K66" s="9" t="str">
+        <f>_xlfn.CONCAT(E66,"_",F66)</f>
+        <v>BHANWAR_LAL_MAKWANA</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N66" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O66" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="P66" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O66" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P66" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q66" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="R66" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67" s="5" t="s">
+      <c r="E67" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="G67" s="9" t="str">
-        <f t="shared" ref="G67:G73" si="1">_xlfn.CONCAT(E67,"_",F67)</f>
-        <v>GHANSHYAM_SINGH_PARIHAR</v>
-      </c>
       <c r="H67" s="5" t="s">
-        <v>381</v>
+        <v>18</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="J67" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K67" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="9" t="str">
+        <f>_xlfn.CONCAT(E67,"_",F67)</f>
+        <v>GHANSHYAM_SINGH_PARIHAR</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="N67" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O67" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O67" s="9" t="s">
+        <v>482</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q67" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="R67" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="5" t="s">
+      <c r="E68" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="F68" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="F68" s="5" t="s">
+      <c r="G68" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="G68" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>RITHU_SINGH_KALESH</v>
-      </c>
       <c r="H68" s="5" t="s">
-        <v>392</v>
+        <v>18</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="J68" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K68" s="5" t="s">
+      <c r="J68" s="5"/>
+      <c r="K68" s="9" t="str">
+        <f>_xlfn.CONCAT(E68,"_",F68)</f>
+        <v>RITHU_SINGH_KALESH</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N68" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O68" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="P68" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O68" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P68" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q68" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="R68" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="5" t="s">
+      <c r="E69" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G69" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G69" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>RAKESH_KUMAR_PANDEY</v>
-      </c>
       <c r="H69" s="5" t="s">
-        <v>397</v>
+        <v>18</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="J69" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K69" s="5" t="s">
+      <c r="J69" s="5"/>
+      <c r="K69" s="9" t="str">
+        <f>_xlfn.CONCAT(E69,"_",F69)</f>
+        <v>RAKESH_KUMAR_PANDEY</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N69" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O69" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="P69" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O69" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P69" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q69" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="R69" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="5" t="s">
+      <c r="E70" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="F70" s="5" t="s">
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="G70" s="9" t="str">
-        <f t="shared" si="1"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="9" t="str">
+        <f>_xlfn.CONCAT(E70,"_",F70)</f>
         <v>Vinod_Kumar_Singh</v>
       </c>
-      <c r="H70" t="s">
-        <v>402</v>
-      </c>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5" t="s">
+      <c r="L70" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N70" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O70" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="P70" t="s">
         <v>401</v>
       </c>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O70" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P70" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q70" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="R70" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G71" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="G71" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Abhay_Singh</v>
-      </c>
       <c r="H71" s="5" t="s">
-        <v>407</v>
+        <v>18</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="J71" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K71" s="5" t="s">
+      <c r="J71" s="5"/>
+      <c r="K71" s="9" t="str">
+        <f>_xlfn.CONCAT(E71,"_",F71)</f>
+        <v>Abhay_Singh</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="P71" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O71" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P71" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q71" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="R71" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="5" t="s">
+      <c r="E72" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="F72" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="F72" s="5" t="s">
+      <c r="G72" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="G72" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>Surekha_Anand_Ahirwar</v>
-      </c>
       <c r="H72" s="5" t="s">
-        <v>407</v>
+        <v>33</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="J72" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="9" t="str">
+        <f>_xlfn.CONCAT(E72,"_",F72)</f>
+        <v>Surekha_Anand_Ahirwar</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="N72" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O72" s="5" t="s">
-        <v>22</v>
+        <v>531</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="P72" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q72" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="R72" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D73" s="5" t="s">
+      <c r="E73" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G73" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>BHOOPENDRA_PRATAP_SINGH</v>
-      </c>
       <c r="H73" s="5" t="s">
-        <v>417</v>
+        <v>18</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="J73" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K73" s="5" t="s">
+      <c r="J73" s="5"/>
+      <c r="K73" s="9" t="str">
+        <f>_xlfn.CONCAT(E73,"_",F73)</f>
+        <v>BHOOPENDRA_PRATAP_SINGH</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N73" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="P73" s="5" t="s">
         <v>416</v>
-      </c>
-      <c r="L73" s="5"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="O73" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P73" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="Q73" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="R73" s="5" t="s">
-        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -6084,10 +5785,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1" t="s">
         <v>418</v>
-      </c>
-      <c r="B1" t="s">
-        <v>419</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -6098,451 +5799,451 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B2" t="s">
         <v>420</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>421</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>422</v>
-      </c>
-      <c r="D2" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
         <v>424</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>425</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>426</v>
-      </c>
-      <c r="D3" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B4" t="s">
         <v>428</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>429</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>430</v>
-      </c>
-      <c r="D4" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>431</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>432</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>433</v>
-      </c>
-      <c r="D5" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C6" t="s">
         <v>435</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>436</v>
-      </c>
-      <c r="D6" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C7" t="s">
         <v>438</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>439</v>
-      </c>
-      <c r="D7" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>440</v>
+      </c>
+      <c r="C8" t="s">
         <v>441</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>442</v>
-      </c>
-      <c r="D8" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C9" t="s">
         <v>444</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>445</v>
-      </c>
-      <c r="D9" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>446</v>
+      </c>
+      <c r="C10" t="s">
         <v>447</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>448</v>
-      </c>
-      <c r="D10" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>449</v>
+      </c>
+      <c r="C11" t="s">
         <v>450</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>451</v>
-      </c>
-      <c r="D11" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" t="s">
         <v>453</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>454</v>
-      </c>
-      <c r="D12" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>455</v>
+      </c>
+      <c r="C13" t="s">
         <v>456</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>457</v>
-      </c>
-      <c r="D13" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>458</v>
+      </c>
+      <c r="C14" t="s">
         <v>459</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>460</v>
-      </c>
-      <c r="D14" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C15" t="s">
         <v>462</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>463</v>
-      </c>
-      <c r="D15" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>464</v>
+      </c>
+      <c r="C16" t="s">
         <v>465</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>466</v>
-      </c>
-      <c r="D16" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>467</v>
+      </c>
+      <c r="C17" t="s">
         <v>468</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>469</v>
-      </c>
-      <c r="D17" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C18" t="s">
         <v>471</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>472</v>
-      </c>
-      <c r="D18" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>473</v>
+      </c>
+      <c r="C19" t="s">
         <v>474</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>475</v>
-      </c>
-      <c r="D19" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>476</v>
+      </c>
+      <c r="C20" t="s">
         <v>477</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>478</v>
-      </c>
-      <c r="D20" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>479</v>
+      </c>
+      <c r="C21" t="s">
         <v>480</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>481</v>
-      </c>
-      <c r="D21" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>482</v>
+      </c>
+      <c r="C22" t="s">
         <v>483</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>484</v>
-      </c>
-      <c r="D22" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>485</v>
+      </c>
+      <c r="C23" t="s">
         <v>486</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>487</v>
-      </c>
-      <c r="D23" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>488</v>
+      </c>
+      <c r="C24" t="s">
         <v>489</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>490</v>
-      </c>
-      <c r="D24" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>491</v>
+      </c>
+      <c r="C25" t="s">
         <v>492</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>493</v>
-      </c>
-      <c r="D25" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>494</v>
+      </c>
+      <c r="C26" t="s">
         <v>495</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>496</v>
-      </c>
-      <c r="D26" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>497</v>
+      </c>
+      <c r="C27" t="s">
         <v>498</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>499</v>
-      </c>
-      <c r="D27" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>500</v>
+      </c>
+      <c r="C28" t="s">
         <v>501</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>502</v>
-      </c>
-      <c r="D28" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
